--- a/data/trans_dic/IP31KM13_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM13_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>91,87%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,79; 94,97</t>
+          <t>85,74; 98,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83,38; 97,34</t>
+          <t>80,65; 95,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79,98; 94,94</t>
+          <t>86,33; 95,49</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,27%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>90,85; 95,32</t>
+          <t>83,21; 92,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83,62; 92,93</t>
+          <t>90,52; 94,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87,39; 93,31</t>
+          <t>87,22; 92,98</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>86,02; 94,18</t>
+          <t>89,74; 96,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90,24; 96,91</t>
+          <t>85,88; 94,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90,15; 95,06</t>
+          <t>89,84; 94,84</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,63%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,92; 94,06</t>
+          <t>86,75; 93,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,79; 93,42</t>
+          <t>90,07; 93,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88,9; 93,12</t>
+          <t>89,4; 93,09</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>59</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>46475</t>
+          <t>50258</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54112</t>
+          <t>41264</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>100587</t>
+          <t>91522</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35328; 51000</t>
+          <t>46054; 52657</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48651; 56794</t>
+          <t>37024; 43739</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89615; 106376</t>
+          <t>86000; 95132</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>583</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>577</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>422313</t>
+          <t>418989</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>454505</t>
+          <t>394322</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>876818</t>
+          <t>813312</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>410477; 430686</t>
+          <t>388124; 432576</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>422492; 469526</t>
+          <t>384389; 402889</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>836402; 893093</t>
+          <t>777177; 828494</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>203</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>132948</t>
+          <t>156764</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>170577</t>
+          <t>133721</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>303524</t>
+          <t>290484</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>125743; 137678</t>
+          <t>149589; 161346</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>163454; 175539</t>
+          <t>126360; 139049</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>295099; 311152</t>
+          <t>281946; 297630</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>845</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>869</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>601736</t>
+          <t>626011</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>679193</t>
+          <t>569306</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1280929</t>
+          <t>1195318</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>586009; 613006</t>
+          <t>595829; 640733</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>638897; 695737</t>
+          <t>556389; 579904</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1241390; 1300440</t>
+          <t>1166263; 1214404</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM13_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM13_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que desayunan lácteos (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>93,56%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>89,89%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>91,87%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>85,74; 98,03</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>80,65; 95,28</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>86,33; 95,49</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>89,83%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>92,85%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>91,27%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>83,21; 92,74</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>90,52; 94,87</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>87,22; 92,98</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>94,05%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>90,88%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>92,56%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>89,74; 96,8</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>85,88; 94,5</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>89,84; 94,84</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>91,15%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>92,16%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>91,63%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>86,75; 93,29</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>90,07; 93,88</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>89,4; 93,09</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.9356424172250527</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.8988990098459848</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.9187110132636941</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>50258</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>41264</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>91522</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.8573858778920915</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.806532436698905</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.8632854642329021</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>46054; 52657</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>37024; 43739</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>86000; 95132</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9802967299968205</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.9528113329124734</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9549497347144552</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1160</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.8983028258273887</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.9285456588963196</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9127156447220744</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>418989</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>394322</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>813312</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.8321286021613981</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.9051549208619591</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.8721648270280434</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>388124; 432576</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>384389; 402889</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>777177; 828494</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9274317836325555</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9487195645879591</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9297532529388151</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>423</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.940476309228129</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.9087983439918813</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.9256238204132365</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>156764</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>133721</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>290484</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.8974319410438948</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.8587749643575566</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.8984194185718374</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>149589; 161346</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>126360; 139049</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>281946; 297630</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.9679650555468478</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9450143825200191</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9483941186708323</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>869</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.9114581644351256</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.9216386457467696</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9162787299405289</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>626011</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>569306</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1195318</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.8675134355668738</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.9007265630549443</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.894006770028775</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>595829; 640733</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>556389; 579904</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1166263; 1214404</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9328919465149366</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9387942199665573</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9309092001485041</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que desayunan lácteos (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>50258</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>41264</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>91522</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>46054</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>37024</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>86000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>52657</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>43739</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>95132</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>577</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>583</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>418989</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>394322</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>813312</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>388124</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>384389</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>777177</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>432576</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>402889</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>828494</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>220</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>203</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>156764</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>133721</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>290484</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>149589</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>126360</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>281946</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>161346</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>139049</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>297630</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>869</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>845</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>626011</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>569306</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>1195318</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>595829</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>556389</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1166263</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>640733</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>579904</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1214404</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>